--- a/AEGIOS - UFLEX SALES 25-26_output.xlsx
+++ b/AEGIOS - UFLEX SALES 25-26_output.xlsx
@@ -582,7 +582,7 @@
     <t xml:space="preserve">Failed: locator.waitFor: Timeout 20000ms exceeded.
 Call log:
 [2m  - waiting for locator('.form-group').filter({ has: locator('label').filter({ hasText: 'Registration Type' }) }).first() to be visible[22m
-[2m    43 × locator resolved to hidden &lt;div _ngcontent-ng-c1973799827="" class="form-group ng-star-inserted"&gt;…&lt;/div&gt;[22m
+[2m    44 × locator resolved to hidden &lt;div _ngcontent-ng-c1973799827="" class="form-group ng-star-inserted"&gt;…&lt;/div&gt;[22m
 </t>
   </si>
   <si>
@@ -6715,7 +6715,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" ht="14.25" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="14.25" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>2</v>
       </c>
